--- a/data/trans_orig/P26-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P26-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158443</t>
+          <t>158731</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205476</t>
+          <t>204372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>209414</t>
+          <t>210985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>258429</t>
+          <t>257492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382079</t>
+          <t>382005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451124</t>
+          <t>448135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437334</t>
+          <t>438438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484367</t>
+          <t>484079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365941</t>
+          <t>366878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>414956</t>
+          <t>413385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>816056</t>
+          <t>819045</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>885101</t>
+          <t>885175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>234294</t>
+          <t>237214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>290207</t>
+          <t>292762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>305658</t>
+          <t>306667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>363898</t>
+          <t>365848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>552059</t>
+          <t>558370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>635016</t>
+          <t>636309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>617026</t>
+          <t>614471</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>672939</t>
+          <t>670019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>526098</t>
+          <t>524148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>584338</t>
+          <t>583329</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1162213</t>
+          <t>1160920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1245170</t>
+          <t>1238859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167024</t>
+          <t>164188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213228</t>
+          <t>211138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199772</t>
+          <t>199176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>247362</t>
+          <t>247224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>377814</t>
+          <t>380628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>446201</t>
+          <t>447909</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>421387</t>
+          <t>423477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467591</t>
+          <t>470427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>376128</t>
+          <t>376266</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>423718</t>
+          <t>424314</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>811903</t>
+          <t>810195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>880290</t>
+          <t>877476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217999</t>
+          <t>217065</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268244</t>
+          <t>268581</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>324573</t>
+          <t>324036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>386201</t>
+          <t>382133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>553271</t>
+          <t>553961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>635581</t>
+          <t>638652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598964</t>
+          <t>598627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>649209</t>
+          <t>650143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>568330</t>
+          <t>572398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>629958</t>
+          <t>630495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1186158</t>
+          <t>1183087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1268468</t>
+          <t>1267778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,59%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>819766</t>
+          <t>824973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>919521</t>
+          <t>926295</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1092109</t>
+          <t>1093745</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1200621</t>
+          <t>1202815</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1943595</t>
+          <t>1943490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2094258</t>
+          <t>2096193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2132345</t>
+          <t>2125571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2232100</t>
+          <t>2226893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1891766</t>
+          <t>1889572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2000278</t>
+          <t>1998642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4049995</t>
+          <t>4048060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4200658</t>
+          <t>4200763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>165327</t>
+          <t>167431</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>211502</t>
+          <t>213818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>221377</t>
+          <t>220784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273089</t>
+          <t>275597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>401689</t>
+          <t>401261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>472679</t>
+          <t>472956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469457</t>
+          <t>467141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>515632</t>
+          <t>513528</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>380451</t>
+          <t>377943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>432163</t>
+          <t>432756</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>861819</t>
+          <t>861542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>932809</t>
+          <t>933237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,93%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>290020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>349967</t>
+          <t>350639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>366260</t>
+          <t>365995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>432258</t>
+          <t>433832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>673673</t>
+          <t>675680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>759453</t>
+          <t>762153</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>631456</t>
+          <t>630784</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>691964</t>
+          <t>691403</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>560067</t>
+          <t>558493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>626065</t>
+          <t>626330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1214294</t>
+          <t>1211594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1300074</t>
+          <t>1298067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210234</t>
+          <t>210668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>262372</t>
+          <t>263289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>274916</t>
+          <t>274806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>330207</t>
+          <t>330977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>498267</t>
+          <t>502490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>580004</t>
+          <t>576559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>454498</t>
+          <t>453581</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506636</t>
+          <t>506202</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>402666</t>
+          <t>401896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457957</t>
+          <t>458067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>869739</t>
+          <t>873184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>951476</t>
+          <t>947253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,34%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>304029</t>
+          <t>302392</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>362357</t>
+          <t>361472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>326439</t>
+          <t>325478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>385910</t>
+          <t>387762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>646710</t>
+          <t>649296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>732970</t>
+          <t>732306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>538869</t>
+          <t>539754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>597197</t>
+          <t>598834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598145</t>
+          <t>596293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>657616</t>
+          <t>658577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1152311</t>
+          <t>1152975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1238571</t>
+          <t>1235985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1030129</t>
+          <t>1027083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1135805</t>
+          <t>1135492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1249274</t>
+          <t>1240770</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1358923</t>
+          <t>1360887</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2301312</t>
+          <t>2297091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2464960</t>
+          <t>2459735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2144672</t>
+          <t>2144985</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2250348</t>
+          <t>2253394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2003869</t>
+          <t>2001905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2113518</t>
+          <t>2122022</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4178310</t>
+          <t>4183535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4341958</t>
+          <t>4346179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135290</t>
+          <t>136252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177443</t>
+          <t>180164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148948</t>
+          <t>148935</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192042</t>
+          <t>192996</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>297959</t>
+          <t>296716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>357517</t>
+          <t>356875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>434604</t>
+          <t>431883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>476757</t>
+          <t>475795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>432308</t>
+          <t>431354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>475402</t>
+          <t>475415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>878881</t>
+          <t>879523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>938439</t>
+          <t>939682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203280</t>
+          <t>202544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257956</t>
+          <t>260171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>222295</t>
+          <t>219661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>276611</t>
+          <t>274480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>437421</t>
+          <t>434046</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>519137</t>
+          <t>514071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>707580</t>
+          <t>705365</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>762256</t>
+          <t>762992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>702932</t>
+          <t>705063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>757248</t>
+          <t>759882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1425943</t>
+          <t>1431009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1507659</t>
+          <t>1511034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>180432</t>
+          <t>177946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>229931</t>
+          <t>231022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>229088</t>
+          <t>227311</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>281895</t>
+          <t>280135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>422513</t>
+          <t>418854</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>494695</t>
+          <t>491852</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>493305</t>
+          <t>492214</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542804</t>
+          <t>545290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450947</t>
+          <t>452707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>503754</t>
+          <t>505531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>961383</t>
+          <t>964226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033565</t>
+          <t>1037224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182105</t>
+          <t>179930</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231270</t>
+          <t>232742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182026</t>
+          <t>179274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>233767</t>
+          <t>231191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378739</t>
+          <t>379406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>450729</t>
+          <t>449327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>618852</t>
+          <t>617380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>668017</t>
+          <t>670192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>712835</t>
+          <t>715411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>764576</t>
+          <t>767328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1345995</t>
+          <t>1347397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1417985</t>
+          <t>1417318</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>744248</t>
+          <t>747042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>846071</t>
+          <t>847666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>824932</t>
+          <t>822229</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>925972</t>
+          <t>926247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1599733</t>
+          <t>1603052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1747684</t>
+          <t>1748846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2304871</t>
+          <t>2303276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2406694</t>
+          <t>2403900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2357365</t>
+          <t>2357090</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2458405</t>
+          <t>2461108</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4686595</t>
+          <t>4685433</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4834546</t>
+          <t>4831227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35297</t>
+          <t>34779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69823</t>
+          <t>70074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44574</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>68884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86224</t>
+          <t>85028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128976</t>
+          <t>128349</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486505</t>
+          <t>486254</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>521031</t>
+          <t>521549</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>534721</t>
+          <t>533912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>558222</t>
+          <t>557776</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1030148</t>
+          <t>1030775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1072900</t>
+          <t>1074096</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94654</t>
+          <t>94488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>665802</t>
+          <t>766248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109030</t>
+          <t>106922</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144408</t>
+          <t>145416</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224605</t>
+          <t>224843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1040506</t>
+          <t>965604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450678</t>
+          <t>350232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1021826</t>
+          <t>1021992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>729027</t>
+          <t>728019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>764405</t>
+          <t>766513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>949409</t>
+          <t>1024311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1765310</t>
+          <t>1765072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58225</t>
+          <t>59934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103614</t>
+          <t>101849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49529</t>
+          <t>55818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151427</t>
+          <t>154725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119820</t>
+          <t>111838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235636</t>
+          <t>232577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>542239</t>
+          <t>544004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>587628</t>
+          <t>585919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>731637</t>
+          <t>728339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>833535</t>
+          <t>827246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1293281</t>
+          <t>1296340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1409097</t>
+          <t>1417079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108904</t>
+          <t>108245</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158228</t>
+          <t>158555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111426</t>
+          <t>112244</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>166048</t>
+          <t>167338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>235349</t>
+          <t>236650</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311630</t>
+          <t>311479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>693092</t>
+          <t>692765</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>742416</t>
+          <t>743075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>839455</t>
+          <t>838165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>894077</t>
+          <t>893259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1545192</t>
+          <t>1545343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1621473</t>
+          <t>1620172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>362671</t>
+          <t>354939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1220357</t>
+          <t>1164886</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348927</t>
+          <t>344940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481007</t>
+          <t>485998</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>781055</t>
+          <t>776418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1741870</t>
+          <t>1717584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1949624</t>
+          <t>2005095</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2807310</t>
+          <t>2815042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2883790</t>
+          <t>2878799</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3015870</t>
+          <t>3019857</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4792908</t>
+          <t>4817194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5753723</t>
+          <t>5758360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P26-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P26-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>158731</t>
+          <t>158803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204372</t>
+          <t>205535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>210985</t>
+          <t>211108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257492</t>
+          <t>258382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382005</t>
+          <t>380858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>448135</t>
+          <t>447912</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438438</t>
+          <t>437275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484079</t>
+          <t>484007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>366878</t>
+          <t>365988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>413385</t>
+          <t>413262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>819045</t>
+          <t>819268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>885175</t>
+          <t>886322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>237214</t>
+          <t>233047</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>292762</t>
+          <t>289451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>306667</t>
+          <t>304451</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>365848</t>
+          <t>363777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>558370</t>
+          <t>555734</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>636309</t>
+          <t>636734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>614471</t>
+          <t>617782</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>670019</t>
+          <t>674186</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>524148</t>
+          <t>526219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>583329</t>
+          <t>585545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1160920</t>
+          <t>1160495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1238859</t>
+          <t>1241495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164188</t>
+          <t>165970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211138</t>
+          <t>210369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199176</t>
+          <t>200741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>247224</t>
+          <t>249209</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>380628</t>
+          <t>380563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>447909</t>
+          <t>450220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423477</t>
+          <t>424246</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>470427</t>
+          <t>468645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>376266</t>
+          <t>374281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>424314</t>
+          <t>422749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>810195</t>
+          <t>807884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>877476</t>
+          <t>877541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217065</t>
+          <t>217517</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268581</t>
+          <t>265017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>324036</t>
+          <t>323832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382133</t>
+          <t>380765</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>553961</t>
+          <t>558138</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>638652</t>
+          <t>634177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598627</t>
+          <t>602191</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>650143</t>
+          <t>649691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>572398</t>
+          <t>573766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>630495</t>
+          <t>630699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1183087</t>
+          <t>1187562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1267778</t>
+          <t>1263601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>824973</t>
+          <t>818869</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>926295</t>
+          <t>923660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1093745</t>
+          <t>1097897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1202815</t>
+          <t>1201372</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1943490</t>
+          <t>1949927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2096193</t>
+          <t>2091256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2125571</t>
+          <t>2128206</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2226893</t>
+          <t>2232997</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1889572</t>
+          <t>1891015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1998642</t>
+          <t>1994490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4048060</t>
+          <t>4052997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4200763</t>
+          <t>4194326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>167431</t>
+          <t>166367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>213818</t>
+          <t>212006</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>220784</t>
+          <t>222102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>275597</t>
+          <t>273179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>401261</t>
+          <t>401608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>472956</t>
+          <t>469326</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>467141</t>
+          <t>468953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>513528</t>
+          <t>514592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377943</t>
+          <t>380361</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>432756</t>
+          <t>431438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>861542</t>
+          <t>865172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>933237</t>
+          <t>932890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,91%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>290020</t>
+          <t>294246</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>350639</t>
+          <t>352955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>365995</t>
+          <t>365016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>433832</t>
+          <t>431063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>675680</t>
+          <t>673286</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>762153</t>
+          <t>764530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>630784</t>
+          <t>628468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>691403</t>
+          <t>687177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558493</t>
+          <t>561262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>626330</t>
+          <t>627309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1211594</t>
+          <t>1209217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1298067</t>
+          <t>1300461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>210668</t>
+          <t>210800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>263289</t>
+          <t>262256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>274806</t>
+          <t>274070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>330977</t>
+          <t>329866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>502490</t>
+          <t>500566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>576559</t>
+          <t>573635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453581</t>
+          <t>454614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>506202</t>
+          <t>506070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>401896</t>
+          <t>403007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458067</t>
+          <t>458803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>873184</t>
+          <t>876108</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>947253</t>
+          <t>949177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>302392</t>
+          <t>303263</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>361472</t>
+          <t>364787</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>325478</t>
+          <t>325655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>387762</t>
+          <t>388454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>649296</t>
+          <t>650444</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>732306</t>
+          <t>736165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539754</t>
+          <t>536439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>598834</t>
+          <t>597963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>596293</t>
+          <t>595601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>658577</t>
+          <t>658400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1152975</t>
+          <t>1149116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1235985</t>
+          <t>1234837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,5%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1027083</t>
+          <t>1019908</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1135492</t>
+          <t>1131297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1240770</t>
+          <t>1243776</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1360887</t>
+          <t>1360681</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2297091</t>
+          <t>2296675</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2459735</t>
+          <t>2459791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2144985</t>
+          <t>2149180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2253394</t>
+          <t>2260569</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2001905</t>
+          <t>2002111</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2122022</t>
+          <t>2119016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4183535</t>
+          <t>4183479</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4346179</t>
+          <t>4346595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136252</t>
+          <t>133940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180164</t>
+          <t>179741</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148935</t>
+          <t>148719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192996</t>
+          <t>190936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>296716</t>
+          <t>297339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>356875</t>
+          <t>355395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431883</t>
+          <t>432306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>475795</t>
+          <t>478107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>431354</t>
+          <t>433414</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>475415</t>
+          <t>475631</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879523</t>
+          <t>881003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>939682</t>
+          <t>939059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,95%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>202544</t>
+          <t>202489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>260171</t>
+          <t>256888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>219661</t>
+          <t>218344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>274480</t>
+          <t>275788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>434046</t>
+          <t>438240</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>514071</t>
+          <t>517468</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>705365</t>
+          <t>708648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>762992</t>
+          <t>763047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>705063</t>
+          <t>703755</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>759882</t>
+          <t>761199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1431009</t>
+          <t>1427612</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1511034</t>
+          <t>1506840</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,47%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177946</t>
+          <t>179210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>231022</t>
+          <t>226418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>227311</t>
+          <t>229250</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>280135</t>
+          <t>282536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>418854</t>
+          <t>420582</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>491852</t>
+          <t>493234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492214</t>
+          <t>496818</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545290</t>
+          <t>544026</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>452707</t>
+          <t>450306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>505531</t>
+          <t>503592</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>964226</t>
+          <t>962844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1037224</t>
+          <t>1035496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,12%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179930</t>
+          <t>182016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>232742</t>
+          <t>230433</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179274</t>
+          <t>183162</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>231191</t>
+          <t>236763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379406</t>
+          <t>380882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>449327</t>
+          <t>454743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>617380</t>
+          <t>619689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>670192</t>
+          <t>668106</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>715411</t>
+          <t>709839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>767328</t>
+          <t>763440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1347397</t>
+          <t>1341981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1417318</t>
+          <t>1415842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,8%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>747042</t>
+          <t>747300</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>847666</t>
+          <t>845332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>822229</t>
+          <t>828639</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>926247</t>
+          <t>927472</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1603052</t>
+          <t>1604204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1748846</t>
+          <t>1744154</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2303276</t>
+          <t>2305610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2403900</t>
+          <t>2403642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2357090</t>
+          <t>2355865</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2461108</t>
+          <t>2454698</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4685433</t>
+          <t>4690125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4831227</t>
+          <t>4830075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>52619</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70074</t>
+          <t>71641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,17 +6604,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>55429</t>
+          <t>60246</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>48264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68884</t>
+          <t>74422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>104201</t>
+          <t>112865</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85028</t>
+          <t>93403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128349</t>
+          <t>137091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>507556</t>
+          <t>550484</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486254</t>
+          <t>531462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>521549</t>
+          <t>564373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,17 +6717,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>547367</t>
+          <t>594287</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>533912</t>
+          <t>580111</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>557776</t>
+          <t>606269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1054923</t>
+          <t>1144771</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1030775</t>
+          <t>1120545</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1074096</t>
+          <t>1164233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>556328</t>
+          <t>603103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>556328</t>
+          <t>603103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>556328</t>
+          <t>603103</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>602796</t>
+          <t>654533</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>602796</t>
+          <t>654533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>602796</t>
+          <t>654533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1159124</t>
+          <t>1257636</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1159124</t>
+          <t>1257636</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1159124</t>
+          <t>1257636</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>325723</t>
+          <t>89121</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94488</t>
+          <t>68133</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>766248</t>
+          <t>115819</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>125182</t>
+          <t>136915</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106922</t>
+          <t>118112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145416</t>
+          <t>161855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>450905</t>
+          <t>226036</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224843</t>
+          <t>198751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>965604</t>
+          <t>258507</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>790757</t>
+          <t>869790</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350232</t>
+          <t>843092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1021992</t>
+          <t>890778</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>748253</t>
+          <t>841611</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>728019</t>
+          <t>816671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>766513</t>
+          <t>860414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1539010</t>
+          <t>1711400</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1024311</t>
+          <t>1678929</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1765072</t>
+          <t>1738685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,74%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1116480</t>
+          <t>958911</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1116480</t>
+          <t>958911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1116480</t>
+          <t>958911</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>873435</t>
+          <t>978526</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>873435</t>
+          <t>978526</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>873435</t>
+          <t>978526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1989915</t>
+          <t>1937436</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1989915</t>
+          <t>1937436</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1989915</t>
+          <t>1937436</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>78356</t>
+          <t>83578</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>62956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101849</t>
+          <t>108249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>110271</t>
+          <t>120395</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55818</t>
+          <t>101210</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154725</t>
+          <t>140589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>188627</t>
+          <t>203973</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111838</t>
+          <t>175779</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>232577</t>
+          <t>240780</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>567497</t>
+          <t>644186</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>544004</t>
+          <t>619515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585919</t>
+          <t>664808</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>772793</t>
+          <t>634091</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>728339</t>
+          <t>613897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>827246</t>
+          <t>653276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1340290</t>
+          <t>1278277</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1296340</t>
+          <t>1241470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1417079</t>
+          <t>1306471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645853</t>
+          <t>727764</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645853</t>
+          <t>727764</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645853</t>
+          <t>727764</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>883064</t>
+          <t>754486</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>883064</t>
+          <t>754486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>883064</t>
+          <t>754486</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1528917</t>
+          <t>1482250</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1528917</t>
+          <t>1482250</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1528917</t>
+          <t>1482250</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>133409</t>
+          <t>141070</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108245</t>
+          <t>118582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>158555</t>
+          <t>168277</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>142509</t>
+          <t>150024</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112244</t>
+          <t>131428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167338</t>
+          <t>173838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>275917</t>
+          <t>291094</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236650</t>
+          <t>259033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311479</t>
+          <t>325394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>717911</t>
+          <t>768325</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>692765</t>
+          <t>741118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>743075</t>
+          <t>790813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>862994</t>
+          <t>871733</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>838165</t>
+          <t>847919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>893259</t>
+          <t>890329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1580905</t>
+          <t>1640058</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1545343</t>
+          <t>1605758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1620172</t>
+          <t>1672119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,59%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>851320</t>
+          <t>909395</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>851320</t>
+          <t>909395</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>851320</t>
+          <t>909395</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1005503</t>
+          <t>1021757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1005503</t>
+          <t>1021757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1005503</t>
+          <t>1021757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1856822</t>
+          <t>1931152</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1856822</t>
+          <t>1931152</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1856822</t>
+          <t>1931152</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>586260</t>
+          <t>366387</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>354939</t>
+          <t>326728</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1164886</t>
+          <t>413423</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>433391</t>
+          <t>467580</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>344940</t>
+          <t>429704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>485998</t>
+          <t>505219</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1019650</t>
+          <t>833968</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>776418</t>
+          <t>778596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1717584</t>
+          <t>892654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2583721</t>
+          <t>2832785</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2005095</t>
+          <t>2785749</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2815042</t>
+          <t>2872444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2931406</t>
+          <t>2941722</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2878799</t>
+          <t>2904083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3019857</t>
+          <t>2979598</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5515128</t>
+          <t>5774506</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4817194</t>
+          <t>5715820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5758360</t>
+          <t>5829878</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3169981</t>
+          <t>3199172</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3169981</t>
+          <t>3199172</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3169981</t>
+          <t>3199172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3364797</t>
+          <t>3409302</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3364797</t>
+          <t>3409302</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3364797</t>
+          <t>3409302</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6534778</t>
+          <t>6608474</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6534778</t>
+          <t>6608474</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6534778</t>
+          <t>6608474</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
